--- a/etf_holdings/2026-10-14_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:34</t>
+          <t>2026-10-14 00:27:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:35</t>
+          <t>2026-10-14 00:27:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:37</t>
+          <t>2026-10-14 00:27:20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-10-14_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:17</t>
+          <t>2026-10-14 01:01:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:19</t>
+          <t>2026-10-14 01:01:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:20</t>
+          <t>2026-10-14 01:01:43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-10-14_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00993A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.97%2490</t>
+          <t>0%2490</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,20 +522,20 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.35%341,000</t>
+          <t>8.26%333,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.35%</t>
+          <t>8.26%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>341000</v>
+        <v>333000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,33 +570,33 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-9.84%5545</t>
+          <t>-0.45%5520</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.84%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5545</v>
+        <v>5520</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.27%106,000</t>
+          <t>6.23%113,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.27%</t>
+          <t>6.23%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>106000</v>
+        <v>113000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,33 +631,33 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.98%1180</t>
+          <t>+0.42%1185</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.98%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.26%518,000</t>
+          <t>6.17%526,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.26%</t>
+          <t>6.17%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>518000</v>
+        <v>526000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.1%3280</t>
+          <t>+1.07%3315</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3280</v>
+        <v>3315</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.73%176,000</t>
+          <t>5.74%176,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.73%</t>
+          <t>5.74%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-1.89%1040</t>
+          <t>+0.96%1050</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-1.89%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.73%464,000</t>
+          <t>4.80%464,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.73%</t>
+          <t>4.80%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-3.1%5940</t>
+          <t>-0.93%5885</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5940</v>
+        <v>5885</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.48%76,000</t>
+          <t>4.49%76,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.48%</t>
+          <t>4.49%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.95%17350</t>
+          <t>+0.86%17500</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>17350</v>
+        <v>17500</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.36%25,600</t>
+          <t>4.42%25,600</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.36%</t>
+          <t>4.42%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.52%2195</t>
+          <t>+4.83%1735</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>+4.83%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2195</v>
+        <v>1735</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.27%195,191</t>
+          <t>4.10%249,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.10%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>195191</v>
+        <v>249000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.61%1655</t>
+          <t>-0.69%1430</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4.61%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1655</v>
+        <v>1430</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.07%244,000</t>
+          <t>4.02%281,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>4.02%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>244000</v>
+        <v>281000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0%1440</t>
+          <t>+1.85%8245</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1440</v>
+        <v>8245</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.89%281,000</t>
+          <t>3.62%45,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.89%</t>
+          <t>3.62%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>281000</v>
+        <v>45000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.06%8095</t>
+          <t>-1.54%480.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>8095</v>
+        <v>480.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.51%45,000</t>
+          <t>2.80%577,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>2.80%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>45000</v>
+        <v>577000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-7.4%488</t>
+          <t>+9.4%349</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>+9.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>488</v>
+        <v>349</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.93%577,000</t>
+          <t>2.68%846,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.68%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>577000</v>
+        <v>846000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+5.28%319</t>
+          <t>+2.72%567</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+5.28%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>319</v>
+        <v>567</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.47%846,000</t>
+          <t>2.34%427,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>846000</v>
+        <v>427000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-4.99%552</t>
+          <t>-3.64%2115</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-4.99%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>552</v>
+        <v>2115</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.30%411,000</t>
+          <t>2.17%99,191</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>411000</v>
+        <v>99191</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:40</t>
+          <t>2026-10-14 21:56:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,33 +1363,33 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-4.48%1600</t>
+          <t>-3.75%1540</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-4.48%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1600</v>
+        <v>1540</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.95%121,000</t>
+          <t>1.99%125,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>121000</v>
+        <v>125000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.75%141.5</t>
+          <t>+0.35%142</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>141.5</v>
+        <v>142</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.87%1,333,000</t>
+          <t>1.88%1,333,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,33 +1485,33 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.89%740</t>
+          <t>+0.95%747</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.82%248,000</t>
+          <t>1.85%252,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>248000</v>
+        <v>252000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.68%7275</t>
+          <t>-5.43%6880</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>7275</v>
+        <v>6880</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.76%25,000</t>
+          <t>1.81%25,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-5%950</t>
+          <t>-1.75%1685</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>950</v>
+        <v>1685</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.67%174,000</t>
+          <t>1.71%100,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>174000</v>
+        <v>100000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>1560中砂</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.16%4525</t>
+          <t>-0.21%948</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4525</v>
+        <v>948</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.51%34,000</t>
+          <t>1.68%178,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>34000</v>
+        <v>178000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-7.18%161.5</t>
+          <t>-1.1%4475</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-7.18%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>161.5</v>
+        <v>4475</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.50%896,000</t>
+          <t>1.48%33,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>896000</v>
+        <v>33000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.42%718</t>
+          <t>-0.56%714</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.43%206,000</t>
+          <t>1.47%206,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-9.92%2725</t>
+          <t>+2.17%165</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-9.92%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2725</v>
+        <v>165</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.34%46,000</t>
+          <t>1.44%896,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>46000</v>
+        <v>896000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+9.81%1175</t>
+          <t>-9.36%1065</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+9.81%</t>
+          <t>-9.36%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1175</v>
+        <v>1065</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.19%116,000</t>
+          <t>1.36%116,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-4.23%2040</t>
+          <t>+5.69%2880</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2040</v>
+        <v>2880</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.15%56,000</t>
+          <t>1.33%49,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>56000</v>
+        <v>49000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3105穩懋</t>
+          <t>6505台塑化</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-4.14%556</t>
+          <t>+0.42%119.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-4.14%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>556</v>
+        <v>119.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.14%204,000</t>
+          <t>1.29%1,092,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>204000</v>
+        <v>1092000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6505台塑化</t>
+          <t>3105穩懋</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+9.68%119</t>
+          <t>+0.18%557</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+9.68%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>119</v>
+        <v>557</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.14%1,092,000</t>
+          <t>1.18%214,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1092000</v>
+        <v>214000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.91%10060</t>
+          <t>+0.49%2050</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>10060</v>
+        <v>2050</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.12%11,000</t>
+          <t>1.14%56,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>11000</v>
+        <v>56000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.64%2210</t>
+          <t>-0.68%2195</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2210</v>
+        <v>2195</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.11%51,000</t>
+          <t>1.12%51,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:41</t>
+          <t>2026-10-14 21:56:54</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,33 +2278,33 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.79%279</t>
+          <t>-0.72%277</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.79%</t>
+          <t>-0.72%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.07%387,000</t>
+          <t>1.10%396,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>387000</v>
+        <v>396000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.63%544</t>
+          <t>-0.55%10005</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>544</v>
+        <v>10005</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.97%183,000</t>
+          <t>1.00%10,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>183000</v>
+        <v>10000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-4.92%1450</t>
+          <t>-1.29%537</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-4.92%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1450</v>
+        <v>537</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.91%62,000</t>
+          <t>0.99%183,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>62000</v>
+        <v>183000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-9.93%508</t>
+          <t>-2.76%1410</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-9.93%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>508</v>
+        <v>1410</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.84%154,000</t>
+          <t>0.92%64,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>154000</v>
+        <v>64000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-2.37%6990</t>
+          <t>+2.95%523</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+2.95%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>6990</v>
+        <v>523</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.76%11,000</t>
+          <t>0.78%154,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>11000</v>
+        <v>154000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,33 +2583,33 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.21%572</t>
+          <t>+5.42%603</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+5.42%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>572</v>
+        <v>603</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.75%134,000</t>
+          <t>0.77%136,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>134000</v>
+        <v>136000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-4.17%276</t>
+          <t>+1.14%7070</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-4.17%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>276</v>
+        <v>7070</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.62%222,000</t>
+          <t>0.76%11,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.76%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>222000</v>
+        <v>11000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3042晶技</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-4.4%195.5</t>
+          <t>+2.54%283</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>+2.54%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>195.5</v>
+        <v>283</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.58%296,000</t>
+          <t>0.62%227,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>296000</v>
+        <v>227000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>3042晶技</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.47%268.5</t>
+          <t>+4.86%205</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+4.86%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>268.5</v>
+        <v>205</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.56%214,000</t>
+          <t>0.60%310,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>214000</v>
+        <v>310000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-5.76%556</t>
+          <t>+3.54%278</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-5.76%</t>
+          <t>+3.54%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>556</v>
+        <v>278</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.55%96,000</t>
+          <t>0.58%219,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>96000</v>
+        <v>219000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,33 +2888,33 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-6.98%2200</t>
+          <t>+2.27%2250</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2200</v>
+        <v>2250</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.52%23,000</t>
+          <t>0.55%25,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>23000</v>
+        <v>25000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-7.69%1140</t>
+          <t>-1.62%547</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-7.69%</t>
+          <t>-1.62%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1140</v>
+        <v>547</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.48%40,000</t>
+          <t>0.54%98,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>40000</v>
+        <v>98000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-3.37%243.5</t>
+          <t>+1.32%1155</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.37%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>243.5</v>
+        <v>1155</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.45%185,000</t>
+          <t>0.48%42,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>185000</v>
+        <v>42000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2027大成鋼</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+1.14%48.8</t>
+          <t>+2.87%250.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+2.87%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>48.8</v>
+        <v>250.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.39%829,000</t>
+          <t>0.46%189,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>829000</v>
+        <v>189000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.52%77.7</t>
+          <t>+0.64%78.2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>77.7</v>
+        <v>78.2</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.39%526,000</t>
+          <t>0.41%526,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:43</t>
+          <t>2026-10-14 21:56:55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,41 +3188,346 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>2027大成鋼</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>+2.46%50</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>+2.46%</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>50</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.40%829,000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.40%</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>829000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:56:57</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>3665貿聯-KY</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-4.03%2260</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>-4.03%</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>2260</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>0.32%14,000</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>0.32%</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-1.11%2235</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-1.11%</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>2235</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.31%14,000</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
         <v>14000</v>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:56:57</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>5347世界</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>+0.57%176</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>+0.57%</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>176</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.31%177,000</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>177000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:56:57</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2368金像電</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>+7.69%1260</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>+7.69%</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>1260</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.30%26,000</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:56:57</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>6271同欣電</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>+0.83%242</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>+0.83%</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>242</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.27%114,000</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>114000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:56:57</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2481強茂</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>+2.47%166</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>+2.47%</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>166</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.26%159,000</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.26%</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>159000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-14_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:53</t>
+          <t>2026-10-14 22:02:26</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:54</t>
+          <t>2026-10-14 22:02:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:55</t>
+          <t>2026-10-14 22:02:28</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:57</t>
+          <t>2026-10-14 22:02:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:57</t>
+          <t>2026-10-14 22:02:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:57</t>
+          <t>2026-10-14 22:02:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:57</t>
+          <t>2026-10-14 22:02:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:57</t>
+          <t>2026-10-14 22:02:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:26</t>
+          <t>2026-10-14 22:32:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:27</t>
+          <t>2026-10-14 22:32:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:28</t>
+          <t>2026-10-14 22:32:55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:30</t>
+          <t>2026-10-14 22:32:56</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:30</t>
+          <t>2026-10-14 22:32:56</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:30</t>
+          <t>2026-10-14 22:32:56</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:30</t>
+          <t>2026-10-14 22:32:56</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:30</t>
+          <t>2026-10-14 22:32:56</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
